--- a/Datas/MonsterGroup.xlsx
+++ b/Datas/MonsterGroup.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>

--- a/Datas/MonsterGroup.xlsx
+++ b/Datas/MonsterGroup.xlsx
@@ -86,7 +86,7 @@
     <t>当前怪物潮的类型</t>
   </si>
   <si>
-    <t>距离下一波的时间</t>
+    <t>多少秒开始</t>
   </si>
   <si>
     <t>怪物产生的间隔</t>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -1526,7 +1526,7 @@
         <v>35</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="1">
         <v>0.5</v>

--- a/Datas/MonsterGroup.xlsx
+++ b/Datas/MonsterGroup.xlsx
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
@@ -1498,7 +1498,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L6" s="1"/>
     </row>
@@ -1532,7 +1532,7 @@
         <v>0.5</v>
       </c>
       <c r="K7" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1"/>
     </row>

--- a/Datas/MonsterGroup.xlsx
+++ b/Datas/MonsterGroup.xlsx
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="1">
         <v>1</v>
